--- a/Project_ETF/ETF_Investment_Portfolio/0056/ETF_Investment_Portfolio_20260729.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/0056/ETF_Investment_Portfolio_20260729.xlsx
@@ -611,12 +611,12 @@
       </c>
       <c r="C21" s="4" t="inlineStr">
         <is>
-          <t>256,893,416</t>
+          <t>257,678,679</t>
         </is>
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>5.90%</t>
+          <t>5.44%</t>
         </is>
       </c>
     </row>
@@ -633,12 +633,12 @@
       </c>
       <c r="C22" s="4" t="inlineStr">
         <is>
-          <t>694,166,236</t>
+          <t>696,194,175</t>
         </is>
       </c>
       <c r="D22" s="4" t="inlineStr">
         <is>
-          <t>4.20%</t>
+          <t>4.34%</t>
         </is>
       </c>
     </row>
@@ -655,12 +655,12 @@
       </c>
       <c r="C23" s="4" t="inlineStr">
         <is>
-          <t>733,686,559</t>
+          <t>735,559,559</t>
         </is>
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>4.15%</t>
+          <t>4.24%</t>
         </is>
       </c>
     </row>
@@ -677,12 +677,12 @@
       </c>
       <c r="C24" s="4" t="inlineStr">
         <is>
-          <t>439,869,690</t>
+          <t>441,154,613</t>
         </is>
       </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
-          <t>4.01%</t>
+          <t>4.08%</t>
         </is>
       </c>
     </row>
@@ -699,100 +699,100 @@
       </c>
       <c r="C25" s="4" t="inlineStr">
         <is>
-          <t>543,584,852</t>
+          <t>545,181,025</t>
         </is>
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>3.93%</t>
+          <t>4.06%</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="3" t="inlineStr">
         <is>
-          <t>3231</t>
+          <t>2357</t>
         </is>
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>緯創</t>
+          <t>華碩</t>
         </is>
       </c>
       <c r="C26" s="4" t="inlineStr">
         <is>
-          <t>157,655,177</t>
+          <t>35,204,709</t>
         </is>
       </c>
       <c r="D26" s="4" t="inlineStr">
         <is>
-          <t>3.92%</t>
+          <t>4.00%</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="inlineStr">
         <is>
-          <t>2382</t>
+          <t>3231</t>
         </is>
       </c>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>廣達</t>
+          <t>緯創</t>
         </is>
       </c>
       <c r="C27" s="4" t="inlineStr">
         <is>
-          <t>84,339,289</t>
+          <t>158,101,219</t>
         </is>
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t>3.86%</t>
+          <t>4.00%</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t>2408</t>
+          <t>2382</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>南亞科</t>
+          <t>廣達</t>
         </is>
       </c>
       <c r="C28" s="4" t="inlineStr">
         <is>
-          <t>66,879,006</t>
+          <t>84,580,902</t>
         </is>
       </c>
       <c r="D28" s="4" t="inlineStr">
         <is>
-          <t>3.84%</t>
+          <t>3.91%</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="inlineStr">
         <is>
-          <t>2357</t>
+          <t>2408</t>
         </is>
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>華碩</t>
+          <t>南亞科</t>
         </is>
       </c>
       <c r="C29" s="4" t="inlineStr">
         <is>
-          <t>35,103,366</t>
+          <t>67,074,305</t>
         </is>
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t>3.77%</t>
+          <t>3.54%</t>
         </is>
       </c>
     </row>
@@ -809,12 +809,12 @@
       </c>
       <c r="C30" s="4" t="inlineStr">
         <is>
-          <t>171,115,189</t>
+          <t>171,644,314</t>
         </is>
       </c>
       <c r="D30" s="4" t="inlineStr">
         <is>
-          <t>3.60%</t>
+          <t>3.33%</t>
         </is>
       </c>
     </row>
@@ -831,12 +831,12 @@
       </c>
       <c r="C31" s="4" t="inlineStr">
         <is>
-          <t>256,253,308</t>
+          <t>257,001,470</t>
         </is>
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t>2.90%</t>
+          <t>3.00%</t>
         </is>
       </c>
     </row>
@@ -853,12 +853,12 @@
       </c>
       <c r="C32" s="4" t="inlineStr">
         <is>
-          <t>95,151,690</t>
+          <t>95,427,416</t>
         </is>
       </c>
       <c r="D32" s="4" t="inlineStr">
         <is>
-          <t>2.78%</t>
+          <t>2.87%</t>
         </is>
       </c>
     </row>
@@ -875,12 +875,12 @@
       </c>
       <c r="C33" s="4" t="inlineStr">
         <is>
-          <t>605,542,731</t>
+          <t>607,316,275</t>
         </is>
       </c>
       <c r="D33" s="4" t="inlineStr">
         <is>
-          <t>2.62%</t>
+          <t>2.64%</t>
         </is>
       </c>
     </row>
@@ -897,12 +897,12 @@
       </c>
       <c r="C34" s="4" t="inlineStr">
         <is>
-          <t>281,662,238</t>
+          <t>282,504,273</t>
         </is>
       </c>
       <c r="D34" s="4" t="inlineStr">
         <is>
-          <t>2.61%</t>
+          <t>2.62%</t>
         </is>
       </c>
     </row>
@@ -919,56 +919,56 @@
       </c>
       <c r="C35" s="4" t="inlineStr">
         <is>
-          <t>23,671,760</t>
+          <t>23,741,812</t>
         </is>
       </c>
       <c r="D35" s="4" t="inlineStr">
         <is>
-          <t>2.53%</t>
+          <t>2.61%</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="3" t="inlineStr">
         <is>
-          <t>2887</t>
+          <t>4904</t>
         </is>
       </c>
       <c r="B36" s="3" t="inlineStr">
         <is>
-          <t>台新新光金</t>
+          <t>遠傳</t>
         </is>
       </c>
       <c r="C36" s="4" t="inlineStr">
         <is>
-          <t>502,152,953</t>
+          <t>157,546,236</t>
         </is>
       </c>
       <c r="D36" s="4" t="inlineStr">
         <is>
-          <t>2.49%</t>
+          <t>2.50%</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="3" t="inlineStr">
         <is>
-          <t>4904</t>
+          <t>2887</t>
         </is>
       </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t>遠傳</t>
+          <t>台新新光金</t>
         </is>
       </c>
       <c r="C37" s="4" t="inlineStr">
         <is>
-          <t>157,081,602</t>
+          <t>503,597,817</t>
         </is>
       </c>
       <c r="D37" s="4" t="inlineStr">
         <is>
-          <t>2.43%</t>
+          <t>2.45%</t>
         </is>
       </c>
     </row>
@@ -985,12 +985,12 @@
       </c>
       <c r="C38" s="4" t="inlineStr">
         <is>
-          <t>442,501,128</t>
+          <t>443,811,615</t>
         </is>
       </c>
       <c r="D38" s="4" t="inlineStr">
         <is>
-          <t>2.34%</t>
+          <t>2.42%</t>
         </is>
       </c>
     </row>
@@ -1007,12 +1007,12 @@
       </c>
       <c r="C39" s="4" t="inlineStr">
         <is>
-          <t>138,882,219</t>
+          <t>139,293,401</t>
         </is>
       </c>
       <c r="D39" s="4" t="inlineStr">
         <is>
-          <t>2.31%</t>
+          <t>2.36%</t>
         </is>
       </c>
     </row>
@@ -1029,51 +1029,51 @@
       </c>
       <c r="C40" s="4" t="inlineStr">
         <is>
-          <t>66,144,077</t>
+          <t>66,336,886</t>
         </is>
       </c>
       <c r="D40" s="4" t="inlineStr">
         <is>
-          <t>2.30%</t>
+          <t>2.35%</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="3" t="inlineStr">
         <is>
-          <t>2303</t>
+          <t>3034</t>
         </is>
       </c>
       <c r="B41" s="3" t="inlineStr">
         <is>
-          <t>聯電</t>
+          <t>聯詠</t>
         </is>
       </c>
       <c r="C41" s="4" t="inlineStr">
         <is>
-          <t>131,262,215</t>
+          <t>28,024,503</t>
         </is>
       </c>
       <c r="D41" s="4" t="inlineStr">
         <is>
-          <t>2.18%</t>
+          <t>2.11%</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="3" t="inlineStr">
         <is>
-          <t>3034</t>
+          <t>2303</t>
         </is>
       </c>
       <c r="B42" s="3" t="inlineStr">
         <is>
-          <t>聯詠</t>
+          <t>聯電</t>
         </is>
       </c>
       <c r="C42" s="4" t="inlineStr">
         <is>
-          <t>27,941,835</t>
+          <t>131,665,346</t>
         </is>
       </c>
       <c r="D42" s="4" t="inlineStr">
@@ -1095,12 +1095,12 @@
       </c>
       <c r="C43" s="4" t="inlineStr">
         <is>
-          <t>70,399,870</t>
+          <t>70,612,516</t>
         </is>
       </c>
       <c r="D43" s="4" t="inlineStr">
         <is>
-          <t>2.00%</t>
+          <t>1.95%</t>
         </is>
       </c>
     </row>
@@ -1117,12 +1117,12 @@
       </c>
       <c r="C44" s="4" t="inlineStr">
         <is>
-          <t>58,106,022</t>
+          <t>58,274,429</t>
         </is>
       </c>
       <c r="D44" s="4" t="inlineStr">
         <is>
-          <t>1.62%</t>
+          <t>1.60%</t>
         </is>
       </c>
     </row>
@@ -1139,12 +1139,12 @@
       </c>
       <c r="C45" s="4" t="inlineStr">
         <is>
-          <t>247,971,240</t>
+          <t>248,705,541</t>
         </is>
       </c>
       <c r="D45" s="4" t="inlineStr">
         <is>
-          <t>1.55%</t>
+          <t>1.54%</t>
         </is>
       </c>
     </row>
@@ -1161,100 +1161,100 @@
       </c>
       <c r="C46" s="4" t="inlineStr">
         <is>
-          <t>123,089,033</t>
+          <t>123,434,479</t>
         </is>
       </c>
       <c r="D46" s="4" t="inlineStr">
         <is>
-          <t>1.50%</t>
+          <t>1.51%</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="3" t="inlineStr">
         <is>
-          <t>3711</t>
+          <t>2376</t>
         </is>
       </c>
       <c r="B47" s="3" t="inlineStr">
         <is>
-          <t>日月光投控</t>
+          <t>技嘉</t>
         </is>
       </c>
       <c r="C47" s="4" t="inlineStr">
         <is>
-          <t>18,554,876</t>
+          <t>30,851,970</t>
         </is>
       </c>
       <c r="D47" s="4" t="inlineStr">
         <is>
-          <t>1.50%</t>
+          <t>1.48%</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="3" t="inlineStr">
         <is>
-          <t>2376</t>
+          <t>5876</t>
         </is>
       </c>
       <c r="B48" s="3" t="inlineStr">
         <is>
-          <t>技嘉</t>
+          <t>上海商銀</t>
         </is>
       </c>
       <c r="C48" s="4" t="inlineStr">
         <is>
-          <t>30,760,919</t>
+          <t>217,893,786</t>
         </is>
       </c>
       <c r="D48" s="4" t="inlineStr">
         <is>
-          <t>1.47%</t>
+          <t>1.44%</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="3" t="inlineStr">
         <is>
-          <t>5876</t>
+          <t>2356</t>
         </is>
       </c>
       <c r="B49" s="3" t="inlineStr">
         <is>
-          <t>上海商銀</t>
+          <t>英業達</t>
         </is>
       </c>
       <c r="C49" s="4" t="inlineStr">
         <is>
-          <t>217,262,820</t>
+          <t>159,357,122</t>
         </is>
       </c>
       <c r="D49" s="4" t="inlineStr">
         <is>
-          <t>1.39%</t>
+          <t>1.43%</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="3" t="inlineStr">
         <is>
-          <t>2356</t>
+          <t>3711</t>
         </is>
       </c>
       <c r="B50" s="3" t="inlineStr">
         <is>
-          <t>英業達</t>
+          <t>日月光投控</t>
         </is>
       </c>
       <c r="C50" s="4" t="inlineStr">
         <is>
-          <t>158,884,769</t>
+          <t>18,609,822</t>
         </is>
       </c>
       <c r="D50" s="4" t="inlineStr">
         <is>
-          <t>1.37%</t>
+          <t>1.39%</t>
         </is>
       </c>
     </row>
@@ -1271,12 +1271,12 @@
       </c>
       <c r="C51" s="4" t="inlineStr">
         <is>
-          <t>2,732,187</t>
+          <t>2,740,321</t>
         </is>
       </c>
       <c r="D51" s="4" t="inlineStr">
         <is>
-          <t>1.32%</t>
+          <t>1.29%</t>
         </is>
       </c>
     </row>
@@ -1293,56 +1293,56 @@
       </c>
       <c r="C52" s="4" t="inlineStr">
         <is>
-          <t>24,984,793</t>
+          <t>25,056,256</t>
         </is>
       </c>
       <c r="D52" s="4" t="inlineStr">
         <is>
-          <t>1.31%</t>
+          <t>1.27%</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="3" t="inlineStr">
         <is>
-          <t>6239</t>
+          <t>3702</t>
         </is>
       </c>
       <c r="B53" s="3" t="inlineStr">
         <is>
-          <t>力成</t>
+          <t>大聯大</t>
         </is>
       </c>
       <c r="C53" s="4" t="inlineStr">
         <is>
-          <t>33,925,168</t>
+          <t>75,439,498</t>
         </is>
       </c>
       <c r="D53" s="4" t="inlineStr">
         <is>
-          <t>1.25%</t>
+          <t>1.19%</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="3" t="inlineStr">
         <is>
-          <t>3702</t>
+          <t>6239</t>
         </is>
       </c>
       <c r="B54" s="3" t="inlineStr">
         <is>
-          <t>大聯大</t>
+          <t>力成</t>
         </is>
       </c>
       <c r="C54" s="4" t="inlineStr">
         <is>
-          <t>75,216,062</t>
+          <t>34,025,598</t>
         </is>
       </c>
       <c r="D54" s="4" t="inlineStr">
         <is>
-          <t>1.21%</t>
+          <t>1.18%</t>
         </is>
       </c>
     </row>
@@ -1359,51 +1359,51 @@
       </c>
       <c r="C55" s="4" t="inlineStr">
         <is>
-          <t>32,645,926</t>
+          <t>32,742,621</t>
         </is>
       </c>
       <c r="D55" s="4" t="inlineStr">
         <is>
-          <t>1.13%</t>
+          <t>1.04%</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="3" t="inlineStr">
         <is>
-          <t>202608TX</t>
+          <t>2324</t>
         </is>
       </c>
       <c r="B56" s="3" t="inlineStr">
         <is>
-          <t>臺股期貨</t>
+          <t>仁寶</t>
         </is>
       </c>
       <c r="C56" s="4" t="inlineStr">
         <is>
-          <t>837</t>
+          <t>200,665,927</t>
         </is>
       </c>
       <c r="D56" s="4" t="inlineStr">
         <is>
-          <t>1.02%</t>
+          <t>1.04%</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="3" t="inlineStr">
         <is>
-          <t>2324</t>
+          <t>2347</t>
         </is>
       </c>
       <c r="B57" s="3" t="inlineStr">
         <is>
-          <t>仁寶</t>
+          <t>聯強</t>
         </is>
       </c>
       <c r="C57" s="4" t="inlineStr">
         <is>
-          <t>200,073,556</t>
+          <t>79,249,791</t>
         </is>
       </c>
       <c r="D57" s="4" t="inlineStr">
@@ -1415,22 +1415,22 @@
     <row r="58">
       <c r="A58" s="3" t="inlineStr">
         <is>
-          <t>2347</t>
+          <t>202608TX</t>
         </is>
       </c>
       <c r="B58" s="3" t="inlineStr">
         <is>
-          <t>聯強</t>
+          <t>臺股期貨</t>
         </is>
       </c>
       <c r="C58" s="4" t="inlineStr">
         <is>
-          <t>79,011,083</t>
+          <t>837</t>
         </is>
       </c>
       <c r="D58" s="4" t="inlineStr">
         <is>
-          <t>0.99%</t>
+          <t>1.01%</t>
         </is>
       </c>
     </row>
@@ -1447,12 +1447,12 @@
       </c>
       <c r="C59" s="4" t="inlineStr">
         <is>
-          <t>38,803,962</t>
+          <t>38,921,241</t>
         </is>
       </c>
       <c r="D59" s="4" t="inlineStr">
         <is>
-          <t>0.79%</t>
+          <t>0.80%</t>
         </is>
       </c>
     </row>
@@ -1469,12 +1469,12 @@
       </c>
       <c r="C60" s="4" t="inlineStr">
         <is>
-          <t>22,705,585</t>
+          <t>22,774,807</t>
         </is>
       </c>
       <c r="D60" s="4" t="inlineStr">
         <is>
-          <t>0.76%</t>
+          <t>0.73%</t>
         </is>
       </c>
     </row>
@@ -1491,56 +1491,56 @@
       </c>
       <c r="C61" s="4" t="inlineStr">
         <is>
-          <t>148,498,127</t>
+          <t>148,944,750</t>
         </is>
       </c>
       <c r="D61" s="4" t="inlineStr">
         <is>
-          <t>0.72%</t>
+          <t>0.73%</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="3" t="inlineStr">
         <is>
-          <t>2474</t>
+          <t>2027</t>
         </is>
       </c>
       <c r="B62" s="3" t="inlineStr">
         <is>
-          <t>可成</t>
+          <t>大成鋼</t>
         </is>
       </c>
       <c r="C62" s="4" t="inlineStr">
         <is>
-          <t>25,564,657</t>
+          <t>108,749,635</t>
         </is>
       </c>
       <c r="D62" s="4" t="inlineStr">
         <is>
-          <t>0.69%</t>
+          <t>0.70%</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="3" t="inlineStr">
         <is>
-          <t>2027</t>
+          <t>2474</t>
         </is>
       </c>
       <c r="B63" s="3" t="inlineStr">
         <is>
-          <t>大成鋼</t>
+          <t>可成</t>
         </is>
       </c>
       <c r="C63" s="4" t="inlineStr">
         <is>
-          <t>108,429,836</t>
+          <t>25,636,369</t>
         </is>
       </c>
       <c r="D63" s="4" t="inlineStr">
         <is>
-          <t>0.67%</t>
+          <t>0.69%</t>
         </is>
       </c>
     </row>
@@ -1557,12 +1557,12 @@
       </c>
       <c r="C64" s="4" t="inlineStr">
         <is>
-          <t>148,842,172</t>
+          <t>149,282,902</t>
         </is>
       </c>
       <c r="D64" s="4" t="inlineStr">
         <is>
-          <t>0.67%</t>
+          <t>0.68%</t>
         </is>
       </c>
     </row>
@@ -1579,12 +1579,12 @@
       </c>
       <c r="C65" s="4" t="inlineStr">
         <is>
-          <t>138,636,078</t>
+          <t>139,044,770</t>
         </is>
       </c>
       <c r="D65" s="4" t="inlineStr">
         <is>
-          <t>0.58%</t>
+          <t>0.59%</t>
         </is>
       </c>
     </row>
@@ -1601,7 +1601,7 @@
       </c>
       <c r="C66" s="4" t="inlineStr">
         <is>
-          <t>22,674,739</t>
+          <t>22,738,317</t>
         </is>
       </c>
       <c r="D66" s="4" t="inlineStr">
@@ -1623,12 +1623,12 @@
       </c>
       <c r="C67" s="4" t="inlineStr">
         <is>
-          <t>32,775,454</t>
+          <t>32,879,536</t>
         </is>
       </c>
       <c r="D67" s="4" t="inlineStr">
         <is>
-          <t>0.49%</t>
+          <t>0.50%</t>
         </is>
       </c>
     </row>
@@ -1645,7 +1645,7 @@
       </c>
       <c r="C68" s="4" t="inlineStr">
         <is>
-          <t>28,600,448</t>
+          <t>28,689,507</t>
         </is>
       </c>
       <c r="D68" s="4" t="inlineStr">
@@ -1667,12 +1667,12 @@
       </c>
       <c r="C69" s="4" t="inlineStr">
         <is>
-          <t>11,030,390</t>
+          <t>11,064,669</t>
         </is>
       </c>
       <c r="D69" s="4" t="inlineStr">
         <is>
-          <t>0.45%</t>
+          <t>0.46%</t>
         </is>
       </c>
     </row>
@@ -1689,12 +1689,12 @@
       </c>
       <c r="C70" s="4" t="inlineStr">
         <is>
-          <t>109,935,639</t>
+          <t>110,273,034</t>
         </is>
       </c>
       <c r="D70" s="4" t="inlineStr">
         <is>
-          <t>0.39%</t>
+          <t>0.40%</t>
         </is>
       </c>
     </row>
@@ -1711,7 +1711,7 @@
       </c>
       <c r="C71" s="4" t="inlineStr">
         <is>
-          <t>13,174,718</t>
+          <t>13,214,724</t>
         </is>
       </c>
       <c r="D71" s="4" t="inlineStr">
